--- a/important_mails_2026-03-23.xlsx
+++ b/important_mails_2026-03-23.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -548,21 +548,73 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
+          <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Add products to Amazon.nl for Pan EU eligibility</t>
+          <t>Submit UK import details by 21/05/2026 to avoid shipping
+ restrictions</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit UK import details by 21/05/2026 to avoid shipping restrictions
+ Hello Weihai EU,
+ Your Amazon.co.uk seller account requires Import Entry Numbers (IENs) for shipments to UK fulfilment centres. You must provide these details by 21/05/2026 to continue creating new UK shipments.
+ Why is this happening?
+ We are taking this action because we identified shipments to Amazon UK fulfilment centres without valid Import Entry Numbers (IENs). UK Customs authorities assign these IENs when goods are imported into the UK. As the seller, you must obtain these numbers from your customs declarant, logistics agent or freight forwarder to maintain UK shipping compliance .
+ Where do I enter my Import Entry Numbers (IEN)?
+ To enter the IENs for your applicable shipments:
+- Go to your Shipping Queue and identify shipments received in Amazon UK FCs.
+- Under “Status”, click the “Import details” text. It will open a pop-up, where you can enter the IENs corresponding to the relevant shipment. You must provide a valid IEN.
+- Save your IEN entry.
+ If you would need to update your IEN, you can follow the above steps again.
+ What happens if I don’t submit these details?
+ You have 60 days after first re</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Add products to Amazon.nl for Pan EU eligibility</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -572,39 +624,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -625,39 +677,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -678,39 +730,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -724,39 +776,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -773,39 +825,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -823,39 +875,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -871,39 +923,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -936,39 +988,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -984,39 +1036,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1032,39 +1084,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1082,39 +1134,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1131,39 +1183,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -1187,39 +1239,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1240,39 +1292,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1296,39 +1348,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1351,39 +1403,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -1399,40 +1451,40 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1448,39 +1500,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1500,39 +1552,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1546,39 +1598,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1598,39 +1650,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1651,39 +1703,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1703,39 +1755,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1755,40 +1807,40 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
@@ -1804,39 +1856,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1862,39 +1914,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Feb 2026 17:52:28 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1915,39 +1967,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -1962,39 +2014,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2018,39 +2070,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2064,39 +2116,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2113,39 +2165,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2165,39 +2217,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2214,39 +2266,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2270,39 +2322,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2322,39 +2374,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 14:12:31 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2374,39 +2426,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 14:54:33 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2422,39 +2474,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:38:32 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2474,39 +2526,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:37:02 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2526,39 +2578,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -2577,39 +2629,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2627,39 +2679,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2681,39 +2733,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2736,39 +2788,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2787,39 +2839,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2838,39 +2890,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -2890,39 +2942,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -2942,39 +2994,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -2992,39 +3044,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3042,39 +3094,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3092,39 +3144,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3143,39 +3195,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3193,40 +3245,40 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3244,39 +3296,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3294,39 +3346,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3344,39 +3396,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3391,39 +3443,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3439,39 +3491,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3489,39 +3541,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3539,39 +3591,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3589,40 +3641,40 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 11:03:26 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 26/04/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 26/04/2026 to avoid shipping restrictions
@@ -3641,39 +3693,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 05:20:21 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3691,39 +3743,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 16:07:02 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit Product Safety Law compliance information for Saudi Arabia</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now submit PSL compliance information through the listing workflow and Manage All Inventory.
@@ -3745,39 +3797,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 20:18:57 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3795,39 +3847,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:12:51 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3846,39 +3898,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:10:23 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3897,39 +3949,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 16:27:54 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Notificaciones automáticas de Amazon Seller Central (favor de no responder a este mensaje) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento para los listados</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 Acción requerida: Información importante sobre tus listados de productos
@@ -3946,39 +3998,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3993,39 +4045,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4041,39 +4093,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4090,40 +4142,40 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4139,39 +4191,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4191,39 +4243,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4239,40 +4291,40 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4288,39 +4340,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4337,39 +4389,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4388,39 +4440,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4438,39 +4490,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4482,39 +4534,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4526,39 +4578,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4570,39 +4622,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4614,39 +4666,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4658,39 +4710,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -4702,39 +4754,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4746,39 +4798,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4790,39 +4842,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -4840,39 +4892,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -4915,39 +4967,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4964,40 +5016,40 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5015,39 +5067,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5065,39 +5117,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5109,39 +5161,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5153,39 +5205,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5204,39 +5256,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5248,39 +5300,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5292,39 +5344,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5336,39 +5388,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5380,39 +5432,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5424,39 +5476,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5468,39 +5520,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5512,39 +5564,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5556,39 +5608,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5600,40 +5652,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5652,39 +5704,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5696,40 +5748,40 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -5741,39 +5793,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5785,39 +5837,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5836,39 +5888,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5880,39 +5932,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5931,39 +5983,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -5975,39 +6027,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6023,40 +6075,40 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6074,39 +6126,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6124,39 +6176,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6172,39 +6224,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6222,39 +6274,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6295,39 +6347,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6345,40 +6397,40 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6396,39 +6448,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6445,39 +6497,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6495,39 +6547,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6545,39 +6597,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6592,39 +6644,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6638,39 +6690,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6686,39 +6738,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6734,39 +6786,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6783,40 +6835,40 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6832,39 +6884,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -6893,39 +6945,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6942,40 +6994,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6992,39 +7044,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7039,40 +7091,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7087,39 +7139,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7134,39 +7186,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7181,39 +7233,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 15:01:07 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7228,39 +7280,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 10:49:26 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7288,39 +7340,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:09:03 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados
@@ -7334,39 +7386,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7389,39 +7441,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7443,39 +7495,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7498,39 +7550,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7553,39 +7605,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7611,39 +7663,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7665,39 +7717,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7721,39 +7773,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 13:32:21 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -7765,40 +7817,40 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7817,40 +7869,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7868,39 +7920,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -7914,39 +7966,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -7964,39 +8016,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8013,39 +8065,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8063,40 +8115,40 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8115,39 +8167,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8163,39 +8215,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8225,40 +8277,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8277,40 +8329,40 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8328,39 +8380,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Upload proof of insurance and explore new best practices guide</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.

--- a/important_mails_2026-03-23.xlsx
+++ b/important_mails_2026-03-23.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,21 +500,79 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
+          <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>FBA reimbursement notification</t>
+          <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed and shipped your removal
+request (UvRxALtvwM) to the address you specified before.
+Return Summary:
+Quantity Requested: 1
+Quantity Successfully Shipped: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being shipped, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-2770073-9467132
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-1178678664727600</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -530,40 +588,40 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -582,39 +640,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -624,39 +682,87 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
+ and eligibility</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Get ready to make this Prime Day your best yet.
+ Hello,
+ Get ready to make this Prime Day your best yet. We’ve made changes to promotion eligibility requirements to ensure deals deliver the value customers expect during our biggest shopping events like Prime Day. We’ve also simplified promotion fees to better align your costs and set FBA inbound dates to ensure your products are Prime-ready for the big event.
+ Promotional eligibility
+ To ensure deals offer substantial value to customers, and in turn drive higher engagement and more sales for you, Prime Exclusive price discounts and deals must now:
+- Be priced at or below the lowest sales price, including promotional prices from previous deals, coupons and price discounts, over the past 60 days .
+- Offer at least 5% off the lowest sales price, including promotional prices from previous deals, coupons and price discounts, over the past 30 days . We’re also giving you more time to act. The deal submission window will be open from March 24, 2026, through June 19, 2026. To schedule a deal, go to Create a new deal .
+ For full eligibility details, go to Deals for events and Price discounts and events .
+ You can use the Deals dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -677,39 +783,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -730,85 +836,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Reminder: Please share your feedback on MCF</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Reminder: Please share your feedback on MCF
-Dear Weihai US,
-As a valued Multi-Channel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than March 19.
-(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_et9BAqtoDGCsCB8?Q_CHL=gl&amp;amp;Q_DL=EMD_Z45pcIhoS9Jgg2Y_et9BAqtoDGCsCB8_CGC_gVqjuURBQB4eTq0&amp;amp;_g_=g
-This submission form is unique to your Seller account and can only be submitted once.
-DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
-Thank you,
-Your Multi-Channel Fulfillment Team
-This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please vi</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -825,39 +885,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -875,39 +935,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -923,39 +983,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -988,39 +1048,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -1036,39 +1096,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1084,39 +1144,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1134,39 +1194,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1183,39 +1243,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -1239,39 +1299,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1292,39 +1352,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1348,39 +1408,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1403,39 +1463,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -1451,40 +1511,86 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Reminder: Please share your feedback on MCF</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Reminder: Please share your feedback on MCF
+Dear Weihai US,
+As a valued Multi-Channel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than March 19.
+(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_et9BAqtoDGCsCB8?Q_CHL=gl&amp;amp;Q_DL=EMD_Z45pcIhoS9Jgg2Y_et9BAqtoDGCsCB8_CGC_gVqjuURBQB4eTq0&amp;amp;_g_=g
+This submission form is unique to your Seller account and can only be submitted once.
+DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
+Thank you,
+Your Multi-Channel Fulfillment Team
+This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please vi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1500,39 +1606,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1552,39 +1658,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1598,39 +1704,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1650,39 +1756,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1703,39 +1809,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1755,39 +1861,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 20:32:33 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (DjHMcVqBnq)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1807,40 +1913,40 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:54:28 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 29.08 in an attempt to settle your Amazon.ca seller account balance.
@@ -1856,39 +1962,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 06:14:30 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (X8HTY1kPjb)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1914,39 +2020,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Feb 2026 17:52:28 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1967,39 +2073,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2014,39 +2120,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2070,39 +2176,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2116,39 +2222,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2165,39 +2271,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2217,39 +2323,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 15:38:46 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2266,39 +2372,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 16:06:24 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2322,39 +2428,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 14:48:41 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2374,39 +2480,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 14:12:31 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2426,39 +2532,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 14:54:33 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2474,39 +2580,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:38:32 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2526,39 +2632,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Feb 2026 13:37:02 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2578,39 +2684,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -2629,39 +2735,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2679,39 +2785,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2733,39 +2839,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -2788,39 +2894,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2839,39 +2945,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2890,39 +2996,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -2942,39 +3048,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -2994,39 +3100,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3044,39 +3150,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3094,39 +3200,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3144,39 +3250,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3195,39 +3301,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 05:28:30 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3245,40 +3351,40 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3296,39 +3402,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3346,39 +3452,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3396,39 +3502,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 15:18:58 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3443,39 +3549,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 09:56:14 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Seller News: February 2026</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3491,39 +3597,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 05:24:39 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3541,39 +3647,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 21:13:50 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai CA,
@@ -3591,39 +3697,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:49 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3641,40 +3747,40 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 11:03:26 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 26/04/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 26/04/2026 to avoid shipping restrictions
@@ -3693,39 +3799,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 05:20:21 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3743,39 +3849,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Feb 2026 16:07:02 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit Product Safety Law compliance information for Saudi Arabia</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now submit PSL compliance information through the listing workflow and Manage All Inventory.
@@ -3797,39 +3903,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 20:18:57 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3847,39 +3953,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:12:51 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3898,39 +4004,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:10:23 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3949,39 +4055,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 16:27:54 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Notificaciones automáticas de Amazon Seller Central (favor de no responder a este mensaje) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento para los listados</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 Acción requerida: Información importante sobre tus listados de productos
@@ -3998,39 +4104,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4045,39 +4151,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4093,39 +4199,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4142,40 +4248,40 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4191,39 +4297,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4243,39 +4349,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4291,40 +4397,40 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4340,39 +4446,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4389,39 +4495,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4440,39 +4546,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4490,39 +4596,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4534,39 +4640,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4578,39 +4684,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4622,39 +4728,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4666,39 +4772,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4710,39 +4816,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -4754,39 +4860,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -4798,39 +4904,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4842,39 +4948,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -4892,39 +4998,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -4967,39 +5073,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5016,40 +5122,40 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5067,39 +5173,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5117,39 +5223,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5161,39 +5267,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5205,39 +5311,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5256,39 +5362,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5300,39 +5406,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5344,39 +5450,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5388,39 +5494,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5432,39 +5538,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5476,39 +5582,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5520,39 +5626,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5564,39 +5670,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5608,39 +5714,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5652,40 +5758,40 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5704,39 +5810,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5748,40 +5854,40 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -5793,39 +5899,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5837,39 +5943,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5888,39 +5994,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5932,39 +6038,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5983,39 +6089,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6027,39 +6133,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6075,40 +6181,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6126,39 +6232,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6176,39 +6282,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6224,39 +6330,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6274,39 +6380,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6347,39 +6453,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6397,40 +6503,40 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6448,39 +6554,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6497,39 +6603,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6547,39 +6653,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6597,39 +6703,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6644,39 +6750,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6690,39 +6796,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6738,39 +6844,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6786,39 +6892,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6835,40 +6941,40 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6884,39 +6990,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -6945,39 +7051,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:58 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6994,40 +7100,40 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:56 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7044,39 +7150,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:18:35 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7091,40 +7197,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:40 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7139,39 +7245,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 19:13:31 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7186,39 +7292,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 18:19:23 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7233,39 +7339,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 15:01:07 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7280,39 +7386,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Feb 2026 10:49:26 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7340,39 +7446,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 17:09:03 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados
@@ -7386,39 +7492,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7441,39 +7547,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7495,39 +7601,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7550,39 +7656,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7605,39 +7711,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7663,39 +7769,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-12</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7717,39 +7823,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7773,39 +7879,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Feb 2026 13:32:21 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -7817,40 +7923,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7869,40 +7975,40 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7920,39 +8026,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -7966,39 +8072,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8016,39 +8122,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8065,39 +8171,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8115,40 +8221,40 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8167,39 +8273,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8215,39 +8321,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8277,40 +8383,40 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8329,40 +8435,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8380,39 +8486,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Feb 2026 01:35:07 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Upload proof of insurance and explore new best practices guide</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Upload proof of commercial liability insurance by March 30, 2026. Review our new best practices guide for mainland China-based sellers to help you avoid common coverage gaps and policy issues.
